--- a/results/Int Task Remove ACC -0.0/Rando_3_permute.xlsx
+++ b/results/Int Task Remove ACC -0.0/Rando_3_permute.xlsx
@@ -440,847 +440,847 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.711288897495794</v>
+        <v>0.6944917151813703</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.711288897495794</v>
+        <v>0.6819852095714165</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7193740090291815</v>
+        <v>0.6888442405683786</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7196874886530059</v>
+        <v>0.6873724597862529</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7239539584367171</v>
+        <v>0.6739775601844566</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7198327301775578</v>
+        <v>0.6685152685152685</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7201462098013822</v>
+        <v>0.6712179712179712</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7170574067125791</v>
+        <v>0.6708548674065915</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7218092252575011</v>
+        <v>0.6708548674065915</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7235944856634512</v>
+        <v>0.6731980973360283</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7229215332663609</v>
+        <v>0.6738976773459533</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7379261930986069</v>
+        <v>0.6710727296934194</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7346122656467484</v>
+        <v>0.6758971690006172</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7364931433896951</v>
+        <v>0.673848053158398</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7384163832439694</v>
+        <v>0.6806102564723254</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7300516817758197</v>
+        <v>0.6887873543045957</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7291039808281188</v>
+        <v>0.6957565267910095</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7213589765313904</v>
+        <v>0.7320233354716114</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7206327689086309</v>
+        <v>0.7297297297297298</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7206327689086309</v>
+        <v>0.7238196100265066</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7209232519577347</v>
+        <v>0.7396727224313431</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7123939434284261</v>
+        <v>0.7344815482746517</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7254414737173358</v>
+        <v>0.7345045448493724</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7398494329528813</v>
+        <v>0.7344319240870965</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7282736834460972</v>
+        <v>0.7189419154936396</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.730903765386524</v>
+        <v>0.67270548649859</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7332131056268987</v>
+        <v>0.6690853414991346</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7201764684523305</v>
+        <v>0.7157042398421709</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6468258675155227</v>
+        <v>0.7223671947809879</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6517459241597172</v>
+        <v>0.7280134590479418</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6153362946466394</v>
+        <v>0.7269277786519166</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.596732065697583</v>
+        <v>0.7288582805824185</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5798961523099454</v>
+        <v>0.7355284975974631</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5798961523099454</v>
+        <v>0.6925345856380338</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5850764333522954</v>
+        <v>0.710378717275269</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5662676559228284</v>
+        <v>0.6957601578291233</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5566224083465463</v>
+        <v>0.6928165962648721</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5632127425230873</v>
+        <v>0.683137458999528</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5753634063978892</v>
+        <v>0.6511371201026372</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5262560366008642</v>
+        <v>0.6490843732223043</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5227121434017986</v>
+        <v>0.6324166979339393</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4960905822974788</v>
+        <v>0.6324166979339393</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4706370051197638</v>
+        <v>0.6312583967756381</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.490889725372484</v>
+        <v>0.5988683264545334</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4822539063918374</v>
+        <v>0.5988683264545334</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4755534307258445</v>
+        <v>0.6166652545962891</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.480278621657932</v>
+        <v>0.6260079156630881</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.480278621657932</v>
+        <v>0.6327701189770155</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4840633737185461</v>
+        <v>0.5826121688190654</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5018252018252018</v>
+        <v>0.5826847895813413</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5706926810375086</v>
+        <v>0.555556093487128</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5427796807107151</v>
+        <v>0.5894905653526343</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5575095919923506</v>
+        <v>0.5894905653526343</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5417944590358383</v>
+        <v>0.5610111230800886</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5383498142118832</v>
+        <v>0.5536752157441813</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.545694193970056</v>
+        <v>0.5581401822781134</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5568112223284637</v>
+        <v>0.5582128030403892</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5690405586957311</v>
+        <v>0.5365681848440469</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5605657157381295</v>
+        <v>0.5352150179736387</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.545141065830721</v>
+        <v>0.529278270657581</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5454581764926593</v>
+        <v>0.5416298519746795</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5487382142554557</v>
+        <v>0.5303336924026579</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5428244635141186</v>
+        <v>0.523990268817855</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5640297260986916</v>
+        <v>0.5265053678846783</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.563112283801939</v>
+        <v>0.5274954309437068</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5725469311676208</v>
+        <v>0.5321213735006839</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5568245361348809</v>
+        <v>0.5213105626898731</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5914670604325777</v>
+        <v>0.5235049200566442</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5983938708076639</v>
+        <v>0.5212730419626972</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5911802084215878</v>
+        <v>0.5207187034773242</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5075307730480144</v>
+        <v>0.5206884448263759</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5067585722758137</v>
+        <v>0.5088839399184226</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5095338957407922</v>
+        <v>0.5084252187700463</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5096065165030682</v>
+        <v>0.5072669176117451</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5076033938102903</v>
+        <v>0.5009174422967526</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5080124907711114</v>
+        <v>0.5020757434550538</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5174737657496278</v>
+        <v>0.5020757434550538</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5210709141743625</v>
+        <v>0.5005313419106523</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5146100870238801</v>
+        <v>0.5004587211483763</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5147783251231527</v>
+        <v>0.5008448215344767</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5048195979230462</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5036504036504037</v>
+        <v>0.5003861003861004</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5015444015444015</v>
+        <v>0.5003861003861004</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5</v>
+        <v>0.5003861003861004</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5</v>
+        <v>0.5003861003861004</v>
       </c>
     </row>
     <row r="87">
@@ -1290,37 +1290,37 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5</v>
+        <v>0.5003861003861004</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4996865203761756</v>
+        <v>0.5003861003861004</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4996865203761756</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4996865203761756</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
